--- a/InputData/hydgn/BHPSbP/BAU Hydrogen Production Shr by Pathway.xlsx
+++ b/InputData/hydgn/BHPSbP/BAU Hydrogen Production Shr by Pathway.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us-analysis\InputData\hydgn\BHPSbP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\hydgn\BHPSbP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A67D7648-F14F-412C-B5F8-99FFC34E7EC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0746773-3F94-4C80-9392-DDC2F80141A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1520" yWindow="1520" windowWidth="14400" windowHeight="9340" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="Evolved" sheetId="4" r:id="rId2"/>
-    <sheet name="BHPSbP" sheetId="2" r:id="rId3"/>
+    <sheet name="BNEF" sheetId="5" r:id="rId2"/>
+    <sheet name="EPS Data" sheetId="6" r:id="rId3"/>
+    <sheet name="BHPSbP" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
   <si>
     <t>BHPSbP BAU Hydrogen Production Shares by Pathway</t>
   </si>
@@ -92,34 +93,70 @@
     <t>hydrocarbon partial oxidation</t>
   </si>
   <si>
-    <t>Evolved Energy</t>
-  </si>
-  <si>
-    <t>https://www.evolved.energy/us-adp-2024</t>
-  </si>
-  <si>
-    <t>Interactive Figure, H2 Production</t>
-  </si>
-  <si>
-    <t>2024 U.S. Annual Decarbonization Perspective</t>
-  </si>
-  <si>
-    <t>Grid-connected electrolysis</t>
-  </si>
-  <si>
-    <t>SMR w/ CC</t>
-  </si>
-  <si>
-    <t>SMR</t>
-  </si>
-  <si>
-    <t>EJ by production pathway</t>
-  </si>
-  <si>
-    <t>% by production pathway</t>
-  </si>
-  <si>
-    <t>Extrapolated</t>
+    <t>% Blue:</t>
+  </si>
+  <si>
+    <t>% Green:</t>
+  </si>
+  <si>
+    <t>Capacity</t>
+  </si>
+  <si>
+    <t>Mt</t>
+  </si>
+  <si>
+    <t>Time (Year)</t>
+  </si>
+  <si>
+    <t>Hydrogen Demand by Sector[transportation sector] : NoSettings</t>
+  </si>
+  <si>
+    <t>Hydrogen Demand by Sector[electricity sector] : NoSettings</t>
+  </si>
+  <si>
+    <t>Hydrogen Demand by Sector[residential buildings sector] : NoSettings</t>
+  </si>
+  <si>
+    <t>Hydrogen Demand by Sector[commercial buildings sector] : NoSettings</t>
+  </si>
+  <si>
+    <t>Hydrogen Demand by Sector[industry sector] : NoSettings</t>
+  </si>
+  <si>
+    <t>Hydrogen Demand by Sector[district heat and hydrogen sector] : NoSettings</t>
+  </si>
+  <si>
+    <t>Hydrogen Demand by Sector[LULUCF sector] : NoSettings</t>
+  </si>
+  <si>
+    <t>Hydrogen Demand by Sector[geoengineering sector] : NoSettings</t>
+  </si>
+  <si>
+    <t>EPS Data</t>
+  </si>
+  <si>
+    <t>BpMMTH BTU per MMT Hydrogen : NoSettings</t>
+  </si>
+  <si>
+    <t>*data for 2030</t>
+  </si>
+  <si>
+    <t>blue</t>
+  </si>
+  <si>
+    <t>green</t>
+  </si>
+  <si>
+    <t>BNEF</t>
+  </si>
+  <si>
+    <t>US Clean Hydrogen Market Outlook</t>
+  </si>
+  <si>
+    <t>https://efiling.energy.ca.gov/GetDocument.aspx?tn=265044</t>
+  </si>
+  <si>
+    <t>pgs. 10, 16</t>
   </si>
 </sst>
 </file>
@@ -129,7 +166,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -153,28 +190,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -186,12 +214,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -202,17 +229,13 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -225,6 +248,99 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>536696</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>70110</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8661492-DC81-408D-BF1C-FD0AB9692D4E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="184150"/>
+          <a:ext cx="6023096" cy="3384810"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>534092</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>171193</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02F6FC29-38EA-45AA-81F7-E95FC535D07A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="606136" y="3752273"/>
+          <a:ext cx="5989320" cy="3360625"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -506,27 +622,27 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B4" s="3">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -536,596 +652,1064 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A53D1DD9-DD63-472A-AC41-88073BAABF04}">
-  <dimension ref="A1:AE14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FCF00DD-FBB5-4F2F-A64F-4218B001AAAE}">
+  <dimension ref="L3:O16"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="3" spans="12:15" x14ac:dyDescent="0.35">
+      <c r="M3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N3">
+        <f>11.71/15.49</f>
+        <v>0.75597159457714658</v>
+      </c>
+    </row>
+    <row r="4" spans="12:15" x14ac:dyDescent="0.35">
+      <c r="M4" t="s">
+        <v>11</v>
+      </c>
+      <c r="N4">
+        <f>1-N3</f>
+        <v>0.24402840542285342</v>
+      </c>
+    </row>
+    <row r="6" spans="12:15" x14ac:dyDescent="0.35">
+      <c r="M6" t="s">
+        <v>12</v>
+      </c>
+      <c r="N6">
+        <v>1.57</v>
+      </c>
+      <c r="O6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="12:15" x14ac:dyDescent="0.35">
+      <c r="M8" t="s">
+        <v>23</v>
+      </c>
+      <c r="N8" s="7">
+        <f>SUM('EPS Data'!I3:I10)/'EPS Data'!I13</f>
+        <v>5.7338269658243561</v>
+      </c>
+      <c r="O8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="12:15" x14ac:dyDescent="0.35">
+      <c r="M10" t="s">
+        <v>10</v>
+      </c>
+      <c r="N10" s="5">
+        <f>N6/N8*N3</f>
+        <v>0.20699532974404683</v>
+      </c>
+    </row>
+    <row r="11" spans="12:15" x14ac:dyDescent="0.35">
+      <c r="M11" t="s">
+        <v>11</v>
+      </c>
+      <c r="N11" s="5">
+        <f>N6/N8*N4</f>
+        <v>6.6818304562980088E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="12:15" x14ac:dyDescent="0.35">
+      <c r="M12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="12:15" x14ac:dyDescent="0.35">
+      <c r="M14">
+        <v>2025</v>
+      </c>
+      <c r="N14">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="15" spans="12:15" x14ac:dyDescent="0.35">
+      <c r="L15" t="s">
+        <v>26</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <f>N10</f>
+        <v>0.20699532974404683</v>
+      </c>
+    </row>
+    <row r="16" spans="12:15" x14ac:dyDescent="0.35">
+      <c r="L16" t="s">
+        <v>27</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <f>N11</f>
+        <v>6.6818304562980088E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED14057-6164-4D1A-BD42-115A681D8E69}">
+  <dimension ref="B2:AC13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.90625" customWidth="1"/>
+    <col min="2" max="2" width="64.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
+    <row r="2" spans="2:29" x14ac:dyDescent="0.35">
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2">
+        <v>2024</v>
+      </c>
+      <c r="D2">
+        <v>2025</v>
+      </c>
+      <c r="E2">
+        <v>2026</v>
+      </c>
+      <c r="F2">
+        <v>2027</v>
+      </c>
+      <c r="G2">
+        <v>2028</v>
+      </c>
+      <c r="H2">
+        <v>2029</v>
+      </c>
+      <c r="I2">
+        <v>2030</v>
+      </c>
+      <c r="J2">
+        <v>2031</v>
+      </c>
+      <c r="K2">
+        <v>2032</v>
+      </c>
+      <c r="L2">
+        <v>2033</v>
+      </c>
+      <c r="M2">
+        <v>2034</v>
+      </c>
+      <c r="N2">
+        <v>2035</v>
+      </c>
+      <c r="O2">
+        <v>2036</v>
+      </c>
+      <c r="P2">
+        <v>2037</v>
+      </c>
+      <c r="Q2">
+        <v>2038</v>
+      </c>
+      <c r="R2">
+        <v>2039</v>
+      </c>
+      <c r="S2">
+        <v>2040</v>
+      </c>
+      <c r="T2">
+        <v>2041</v>
+      </c>
+      <c r="U2">
+        <v>2042</v>
+      </c>
+      <c r="V2">
+        <v>2043</v>
+      </c>
+      <c r="W2">
+        <v>2044</v>
+      </c>
+      <c r="X2">
+        <v>2045</v>
+      </c>
+      <c r="Y2">
+        <v>2046</v>
+      </c>
+      <c r="Z2">
+        <v>2047</v>
+      </c>
+      <c r="AA2">
+        <v>2048</v>
+      </c>
+      <c r="AB2">
+        <v>2049</v>
+      </c>
+      <c r="AC2">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="3" spans="2:29" x14ac:dyDescent="0.35">
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="6">
+        <v>503573000000</v>
+      </c>
+      <c r="D3" s="6">
+        <v>478265000000</v>
+      </c>
+      <c r="E3" s="6">
+        <v>448968000000</v>
+      </c>
+      <c r="F3" s="6">
+        <v>417873000000</v>
+      </c>
+      <c r="G3" s="6">
+        <v>385901000000</v>
+      </c>
+      <c r="H3" s="6">
+        <v>353868000000</v>
+      </c>
+      <c r="I3" s="6">
+        <v>321799000000</v>
+      </c>
+      <c r="J3" s="6">
+        <v>289522000000</v>
+      </c>
+      <c r="K3" s="6">
+        <v>256628000000</v>
+      </c>
+      <c r="L3" s="6">
+        <v>223769000000</v>
+      </c>
+      <c r="M3" s="6">
+        <v>190918000000</v>
+      </c>
+      <c r="N3" s="6">
+        <v>158037000000</v>
+      </c>
+      <c r="O3" s="6">
+        <v>126326000000</v>
+      </c>
+      <c r="P3" s="6">
+        <v>94801800000</v>
+      </c>
+      <c r="Q3" s="6">
+        <v>63274700000</v>
+      </c>
+      <c r="R3" s="6">
+        <v>31607500000</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:29" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4" s="6">
+        <v>99731900000</v>
+      </c>
+      <c r="L4" s="6">
+        <v>199464000000</v>
+      </c>
+      <c r="M4" s="6">
+        <v>199464000000</v>
+      </c>
+      <c r="N4" s="6">
+        <v>199464000000</v>
+      </c>
+      <c r="O4" s="6">
+        <v>99731900000</v>
+      </c>
+      <c r="P4" s="6">
+        <v>99731900000</v>
+      </c>
+      <c r="Q4" s="6">
+        <v>99731900000</v>
+      </c>
+      <c r="R4" s="6">
+        <v>99731900000</v>
+      </c>
+      <c r="S4" s="6">
+        <v>99731900000</v>
+      </c>
+      <c r="T4" s="6">
+        <v>199464000000</v>
+      </c>
+      <c r="U4" s="6">
+        <v>199464000000</v>
+      </c>
+      <c r="V4" s="6">
+        <v>199464000000</v>
+      </c>
+      <c r="W4" s="6">
+        <v>299196000000</v>
+      </c>
+      <c r="X4" s="6">
+        <v>398928000000</v>
+      </c>
+      <c r="Y4" s="6">
+        <v>897587000000</v>
+      </c>
+      <c r="Z4" s="6">
+        <v>1396250000000</v>
+      </c>
+      <c r="AA4" s="6">
+        <v>1595710000000</v>
+      </c>
+      <c r="AB4" s="6">
+        <v>1894910000000</v>
+      </c>
+      <c r="AC4" s="6">
+        <v>2293830000000</v>
+      </c>
+    </row>
+    <row r="5" spans="2:29" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
         <v>17</v>
       </c>
-      <c r="B1">
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:29" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:29" x14ac:dyDescent="0.35">
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="6">
+        <v>766434000000000</v>
+      </c>
+      <c r="D7" s="6">
+        <v>761811000000000</v>
+      </c>
+      <c r="E7" s="6">
+        <v>767823000000000</v>
+      </c>
+      <c r="F7" s="6">
+        <v>770612000000000</v>
+      </c>
+      <c r="G7" s="6">
+        <v>759357000000000</v>
+      </c>
+      <c r="H7" s="6">
+        <v>761580000000000</v>
+      </c>
+      <c r="I7" s="6">
+        <v>770941000000000</v>
+      </c>
+      <c r="J7" s="6">
+        <v>778058000000000</v>
+      </c>
+      <c r="K7" s="6">
+        <v>789035000000000</v>
+      </c>
+      <c r="L7" s="6">
+        <v>797316000000000</v>
+      </c>
+      <c r="M7" s="6">
+        <v>800662000000000</v>
+      </c>
+      <c r="N7" s="6">
+        <v>804543000000000</v>
+      </c>
+      <c r="O7" s="6">
+        <v>810367000000000</v>
+      </c>
+      <c r="P7" s="6">
+        <v>815126000000000</v>
+      </c>
+      <c r="Q7" s="6">
+        <v>815739000000000</v>
+      </c>
+      <c r="R7" s="6">
+        <v>816504000000000</v>
+      </c>
+      <c r="S7" s="6">
+        <v>817544000000000</v>
+      </c>
+      <c r="T7" s="6">
+        <v>817593000000000</v>
+      </c>
+      <c r="U7" s="6">
+        <v>812498000000000</v>
+      </c>
+      <c r="V7" s="6">
+        <v>808775000000000</v>
+      </c>
+      <c r="W7" s="6">
+        <v>809511000000000</v>
+      </c>
+      <c r="X7" s="6">
+        <v>811900000000000</v>
+      </c>
+      <c r="Y7" s="6">
+        <v>812341000000000</v>
+      </c>
+      <c r="Z7" s="6">
+        <v>805955000000000</v>
+      </c>
+      <c r="AA7" s="6">
+        <v>798030000000000</v>
+      </c>
+      <c r="AB7" s="6">
+        <v>794455000000000</v>
+      </c>
+      <c r="AC7" s="6">
+        <v>794974000000000</v>
+      </c>
+    </row>
+    <row r="8" spans="2:29" x14ac:dyDescent="0.35">
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:29" x14ac:dyDescent="0.35">
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:29" x14ac:dyDescent="0.35">
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:29" x14ac:dyDescent="0.35">
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12">
+        <v>2024</v>
+      </c>
+      <c r="D12">
         <v>2025</v>
       </c>
-      <c r="C1">
+      <c r="E12">
+        <v>2026</v>
+      </c>
+      <c r="F12">
+        <v>2027</v>
+      </c>
+      <c r="G12">
+        <v>2028</v>
+      </c>
+      <c r="H12">
+        <v>2029</v>
+      </c>
+      <c r="I12">
         <v>2030</v>
       </c>
-      <c r="D1">
+      <c r="J12">
+        <v>2031</v>
+      </c>
+      <c r="K12">
+        <v>2032</v>
+      </c>
+      <c r="L12">
+        <v>2033</v>
+      </c>
+      <c r="M12">
+        <v>2034</v>
+      </c>
+      <c r="N12">
         <v>2035</v>
       </c>
-    </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2">
-        <v>0.253</v>
-      </c>
-      <c r="D2">
-        <v>1.02</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3">
-        <v>6.0999999999999999E-2</v>
-      </c>
-      <c r="D3">
-        <v>4.4999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4">
-        <v>1.323</v>
-      </c>
-      <c r="C4">
-        <v>1.181</v>
-      </c>
-      <c r="D4">
-        <v>0.71</v>
-      </c>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A6" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6">
-        <v>2025</v>
-      </c>
-      <c r="C6">
-        <v>2030</v>
-      </c>
-      <c r="D6">
-        <v>2035</v>
-      </c>
-    </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="8">
-        <f>B2/SUM(B$2:B$4)</f>
-        <v>0</v>
-      </c>
-      <c r="C7" s="8">
-        <f t="shared" ref="C7:D7" si="0">C2/SUM(C$2:C$4)</f>
-        <v>0.16923076923076921</v>
-      </c>
-      <c r="D7" s="8">
-        <f t="shared" si="0"/>
-        <v>0.57464788732394367</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="8">
-        <f t="shared" ref="B8:D9" si="1">B3/SUM(B$2:B$4)</f>
-        <v>0</v>
-      </c>
-      <c r="C8" s="8">
-        <f t="shared" si="1"/>
-        <v>4.0802675585284276E-2</v>
-      </c>
-      <c r="D8" s="8">
-        <f t="shared" si="1"/>
-        <v>2.5352112676056339E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="8">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C9" s="8">
-        <f t="shared" si="1"/>
-        <v>0.78996655518394643</v>
-      </c>
-      <c r="D9" s="8">
-        <f t="shared" si="1"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A11" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11">
-        <v>2021</v>
-      </c>
-      <c r="C11">
-        <v>2022</v>
-      </c>
-      <c r="D11">
-        <v>2023</v>
-      </c>
-      <c r="E11">
-        <v>2024</v>
-      </c>
-      <c r="F11">
-        <v>2025</v>
-      </c>
-      <c r="G11">
-        <v>2026</v>
-      </c>
-      <c r="H11">
-        <v>2027</v>
-      </c>
-      <c r="I11">
-        <v>2028</v>
-      </c>
-      <c r="J11">
-        <v>2029</v>
-      </c>
-      <c r="K11">
-        <v>2030</v>
-      </c>
-      <c r="L11">
-        <v>2031</v>
-      </c>
-      <c r="M11">
-        <v>2032</v>
-      </c>
-      <c r="N11">
-        <v>2033</v>
-      </c>
-      <c r="O11">
-        <v>2034</v>
-      </c>
-      <c r="P11">
-        <v>2035</v>
-      </c>
-      <c r="Q11">
+      <c r="O12">
         <v>2036</v>
       </c>
-      <c r="R11">
+      <c r="P12">
         <v>2037</v>
       </c>
-      <c r="S11">
+      <c r="Q12">
         <v>2038</v>
       </c>
-      <c r="T11">
+      <c r="R12">
         <v>2039</v>
       </c>
-      <c r="U11">
+      <c r="S12">
         <v>2040</v>
       </c>
-      <c r="V11">
+      <c r="T12">
         <v>2041</v>
       </c>
-      <c r="W11">
+      <c r="U12">
         <v>2042</v>
       </c>
-      <c r="X11">
+      <c r="V12">
         <v>2043</v>
       </c>
-      <c r="Y11">
+      <c r="W12">
         <v>2044</v>
       </c>
-      <c r="Z11">
+      <c r="X12">
         <v>2045</v>
       </c>
-      <c r="AA11">
+      <c r="Y12">
         <v>2046</v>
       </c>
-      <c r="AB11">
+      <c r="Z12">
         <v>2047</v>
       </c>
-      <c r="AC11">
+      <c r="AA12">
         <v>2048</v>
       </c>
-      <c r="AD11">
+      <c r="AB12">
         <v>2049</v>
       </c>
-      <c r="AE11">
+      <c r="AC12">
         <v>2050</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="9">
-        <f>$B7</f>
-        <v>0</v>
-      </c>
-      <c r="C12" s="9">
-        <f t="shared" ref="C12:E12" si="2">$B7</f>
-        <v>0</v>
-      </c>
-      <c r="D12" s="9">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E12" s="9">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F12" s="9">
-        <f t="shared" ref="F12" si="3">$B7</f>
-        <v>0</v>
-      </c>
-      <c r="G12" s="9" cm="1">
-        <f t="array" ref="G12">TREND($B7:$C7,$B$6:$C$6,G$11)</f>
-        <v>3.3846153846155858E-2</v>
-      </c>
-      <c r="H12" s="9" cm="1">
-        <f t="array" ref="H12">TREND($B7:$C7,$B$6:$C$6,H$11)</f>
-        <v>6.7692307692311715E-2</v>
-      </c>
-      <c r="I12" s="9" cm="1">
-        <f t="array" ref="I12">TREND($B7:$C7,$B$6:$C$6,I$11)</f>
-        <v>0.10153846153846757</v>
-      </c>
-      <c r="J12" s="9" cm="1">
-        <f t="array" ref="J12">TREND($B7:$C7,$B$6:$C$6,J$11)</f>
-        <v>0.13538461538462343</v>
-      </c>
-      <c r="K12" s="9" cm="1">
-        <f t="array" ref="K12">TREND($B7:$C7,$B$6:$C$6,K$11)</f>
-        <v>0.16923076923077929</v>
-      </c>
-      <c r="L12" s="9" cm="1">
-        <f t="array" ref="L12">TREND($C7:$D7,$C$6:$D$6,L$11)</f>
-        <v>0.25031419284943013</v>
-      </c>
-      <c r="M12" s="9" cm="1">
-        <f t="array" ref="M12">TREND($C7:$D7,$C$6:$D$6,M$11)</f>
-        <v>0.33139761646805255</v>
-      </c>
-      <c r="N12" s="9" cm="1">
-        <f t="array" ref="N12">TREND($C7:$D7,$C$6:$D$6,N$11)</f>
-        <v>0.41248104008667497</v>
-      </c>
-      <c r="O12" s="9" cm="1">
-        <f t="array" ref="O12">TREND($C7:$D7,$C$6:$D$6,O$11)</f>
-        <v>0.49356446370532581</v>
-      </c>
-      <c r="P12" s="9" cm="1">
-        <f t="array" ref="P12">TREND($C7:$D7,$C$6:$D$6,P$11)</f>
-        <v>0.57464788732394823</v>
-      </c>
-      <c r="Q12" s="9">
-        <f>P12</f>
-        <v>0.57464788732394823</v>
-      </c>
-      <c r="R12" s="9">
-        <f t="shared" ref="R12:AE12" si="4">Q12</f>
-        <v>0.57464788732394823</v>
-      </c>
-      <c r="S12" s="9">
-        <f t="shared" si="4"/>
-        <v>0.57464788732394823</v>
-      </c>
-      <c r="T12" s="9">
-        <f t="shared" si="4"/>
-        <v>0.57464788732394823</v>
-      </c>
-      <c r="U12" s="9">
-        <f t="shared" si="4"/>
-        <v>0.57464788732394823</v>
-      </c>
-      <c r="V12" s="9">
-        <f t="shared" si="4"/>
-        <v>0.57464788732394823</v>
-      </c>
-      <c r="W12" s="9">
-        <f t="shared" si="4"/>
-        <v>0.57464788732394823</v>
-      </c>
-      <c r="X12" s="9">
-        <f t="shared" si="4"/>
-        <v>0.57464788732394823</v>
-      </c>
-      <c r="Y12" s="9">
-        <f t="shared" si="4"/>
-        <v>0.57464788732394823</v>
-      </c>
-      <c r="Z12" s="9">
-        <f t="shared" si="4"/>
-        <v>0.57464788732394823</v>
-      </c>
-      <c r="AA12" s="9">
-        <f t="shared" si="4"/>
-        <v>0.57464788732394823</v>
-      </c>
-      <c r="AB12" s="9">
-        <f t="shared" si="4"/>
-        <v>0.57464788732394823</v>
-      </c>
-      <c r="AC12" s="9">
-        <f t="shared" si="4"/>
-        <v>0.57464788732394823</v>
-      </c>
-      <c r="AD12" s="9">
-        <f t="shared" si="4"/>
-        <v>0.57464788732394823</v>
-      </c>
-      <c r="AE12" s="9">
-        <f t="shared" si="4"/>
-        <v>0.57464788732394823</v>
-      </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="9">
-        <f t="shared" ref="B13:E14" si="5">$B8</f>
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="D13" s="9">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="E13" s="9">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F13" s="9">
-        <f t="shared" ref="F13" si="6">$B8</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="9" cm="1">
-        <f t="array" ref="G13">TREND($B8:$C8,$B$6:$C$6,G$11)</f>
-        <v>8.1605351170566109E-3</v>
-      </c>
-      <c r="H13" s="9" cm="1">
-        <f t="array" ref="H13">TREND($B8:$C8,$B$6:$C$6,H$11)</f>
-        <v>1.6321070234113222E-2</v>
-      </c>
-      <c r="I13" s="9" cm="1">
-        <f t="array" ref="I13">TREND($B8:$C8,$B$6:$C$6,I$11)</f>
-        <v>2.4481605351169833E-2</v>
-      </c>
-      <c r="J13" s="9" cm="1">
-        <f t="array" ref="J13">TREND($B8:$C8,$B$6:$C$6,J$11)</f>
-        <v>3.2642140468226444E-2</v>
-      </c>
-      <c r="K13" s="9" cm="1">
-        <f t="array" ref="K13">TREND($B8:$C8,$B$6:$C$6,K$11)</f>
-        <v>4.0802675585283055E-2</v>
-      </c>
-      <c r="L13" s="9" cm="1">
-        <f t="array" ref="L13">TREND($C8:$D8,$C$6:$D$6,L$11)</f>
-        <v>3.7712563003438504E-2</v>
-      </c>
-      <c r="M13" s="9" cm="1">
-        <f t="array" ref="M13">TREND($C8:$D8,$C$6:$D$6,M$11)</f>
-        <v>3.4622450421593065E-2</v>
-      </c>
-      <c r="N13" s="9" cm="1">
-        <f t="array" ref="N13">TREND($C8:$D8,$C$6:$D$6,N$11)</f>
-        <v>3.1532337839747626E-2</v>
-      </c>
-      <c r="O13" s="9" cm="1">
-        <f t="array" ref="O13">TREND($C8:$D8,$C$6:$D$6,O$11)</f>
-        <v>2.8442225257901299E-2</v>
-      </c>
-      <c r="P13" s="9" cm="1">
-        <f t="array" ref="P13">TREND($C8:$D8,$C$6:$D$6,P$11)</f>
-        <v>2.535211267605586E-2</v>
-      </c>
-      <c r="Q13" s="9">
-        <f t="shared" ref="Q13:AE14" si="7">P13</f>
-        <v>2.535211267605586E-2</v>
-      </c>
-      <c r="R13" s="9">
-        <f t="shared" si="7"/>
-        <v>2.535211267605586E-2</v>
-      </c>
-      <c r="S13" s="9">
-        <f t="shared" si="7"/>
-        <v>2.535211267605586E-2</v>
-      </c>
-      <c r="T13" s="9">
-        <f t="shared" si="7"/>
-        <v>2.535211267605586E-2</v>
-      </c>
-      <c r="U13" s="9">
-        <f t="shared" si="7"/>
-        <v>2.535211267605586E-2</v>
-      </c>
-      <c r="V13" s="9">
-        <f t="shared" si="7"/>
-        <v>2.535211267605586E-2</v>
-      </c>
-      <c r="W13" s="9">
-        <f t="shared" si="7"/>
-        <v>2.535211267605586E-2</v>
-      </c>
-      <c r="X13" s="9">
-        <f t="shared" si="7"/>
-        <v>2.535211267605586E-2</v>
-      </c>
-      <c r="Y13" s="9">
-        <f t="shared" si="7"/>
-        <v>2.535211267605586E-2</v>
-      </c>
-      <c r="Z13" s="9">
-        <f t="shared" si="7"/>
-        <v>2.535211267605586E-2</v>
-      </c>
-      <c r="AA13" s="9">
-        <f t="shared" si="7"/>
-        <v>2.535211267605586E-2</v>
-      </c>
-      <c r="AB13" s="9">
-        <f t="shared" si="7"/>
-        <v>2.535211267605586E-2</v>
-      </c>
-      <c r="AC13" s="9">
-        <f t="shared" si="7"/>
-        <v>2.535211267605586E-2</v>
-      </c>
-      <c r="AD13" s="9">
-        <f t="shared" si="7"/>
-        <v>2.535211267605586E-2</v>
-      </c>
-      <c r="AE13" s="9">
-        <f t="shared" si="7"/>
-        <v>2.535211267605586E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="9">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="C14" s="9">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="D14" s="9">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="E14" s="9">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="F14" s="9">
-        <f t="shared" ref="F14" si="8">$B9</f>
-        <v>1</v>
-      </c>
-      <c r="G14" s="9" cm="1">
-        <f t="array" ref="G14">TREND($B9:$C9,$B$6:$C$6,G$11)</f>
-        <v>0.95799331103678753</v>
-      </c>
-      <c r="H14" s="9" cm="1">
-        <f t="array" ref="H14">TREND($B9:$C9,$B$6:$C$6,H$11)</f>
-        <v>0.91598662207357506</v>
-      </c>
-      <c r="I14" s="9" cm="1">
-        <f t="array" ref="I14">TREND($B9:$C9,$B$6:$C$6,I$11)</f>
-        <v>0.87397993311037681</v>
-      </c>
-      <c r="J14" s="9" cm="1">
-        <f t="array" ref="J14">TREND($B9:$C9,$B$6:$C$6,J$11)</f>
-        <v>0.83197324414716434</v>
-      </c>
-      <c r="K14" s="9" cm="1">
-        <f t="array" ref="K14">TREND($B9:$C9,$B$6:$C$6,K$11)</f>
-        <v>0.78996655518395187</v>
-      </c>
-      <c r="L14" s="9" cm="1">
-        <f t="array" ref="L14">TREND($C9:$D9,$C$6:$D$6,L$11)</f>
-        <v>0.711973244147174</v>
-      </c>
-      <c r="M14" s="9" cm="1">
-        <f t="array" ref="M14">TREND($C9:$D9,$C$6:$D$6,M$11)</f>
-        <v>0.63397993311036771</v>
-      </c>
-      <c r="N14" s="9" cm="1">
-        <f t="array" ref="N14">TREND($C9:$D9,$C$6:$D$6,N$11)</f>
-        <v>0.55598662207358984</v>
-      </c>
-      <c r="O14" s="9" cm="1">
-        <f t="array" ref="O14">TREND($C9:$D9,$C$6:$D$6,O$11)</f>
-        <v>0.47799331103681197</v>
-      </c>
-      <c r="P14" s="9" cm="1">
-        <f t="array" ref="P14">TREND($C9:$D9,$C$6:$D$6,P$11)</f>
-        <v>0.40000000000000568</v>
-      </c>
-      <c r="Q14" s="9">
-        <f t="shared" si="7"/>
-        <v>0.40000000000000568</v>
-      </c>
-      <c r="R14" s="9">
-        <f t="shared" si="7"/>
-        <v>0.40000000000000568</v>
-      </c>
-      <c r="S14" s="9">
-        <f t="shared" si="7"/>
-        <v>0.40000000000000568</v>
-      </c>
-      <c r="T14" s="9">
-        <f t="shared" si="7"/>
-        <v>0.40000000000000568</v>
-      </c>
-      <c r="U14" s="9">
-        <f t="shared" si="7"/>
-        <v>0.40000000000000568</v>
-      </c>
-      <c r="V14" s="9">
-        <f t="shared" si="7"/>
-        <v>0.40000000000000568</v>
-      </c>
-      <c r="W14" s="9">
-        <f t="shared" si="7"/>
-        <v>0.40000000000000568</v>
-      </c>
-      <c r="X14" s="9">
-        <f t="shared" si="7"/>
-        <v>0.40000000000000568</v>
-      </c>
-      <c r="Y14" s="9">
-        <f t="shared" si="7"/>
-        <v>0.40000000000000568</v>
-      </c>
-      <c r="Z14" s="9">
-        <f t="shared" si="7"/>
-        <v>0.40000000000000568</v>
-      </c>
-      <c r="AA14" s="9">
-        <f t="shared" si="7"/>
-        <v>0.40000000000000568</v>
-      </c>
-      <c r="AB14" s="9">
-        <f t="shared" si="7"/>
-        <v>0.40000000000000568</v>
-      </c>
-      <c r="AC14" s="9">
-        <f t="shared" si="7"/>
-        <v>0.40000000000000568</v>
-      </c>
-      <c r="AD14" s="9">
-        <f t="shared" si="7"/>
-        <v>0.40000000000000568</v>
-      </c>
-      <c r="AE14" s="9">
-        <f t="shared" si="7"/>
-        <v>0.40000000000000568</v>
+    <row r="13" spans="2:29" x14ac:dyDescent="0.35">
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="6">
+        <v>134511000000000</v>
+      </c>
+      <c r="D13" s="6">
+        <v>134511000000000</v>
+      </c>
+      <c r="E13" s="6">
+        <v>134511000000000</v>
+      </c>
+      <c r="F13" s="6">
+        <v>134511000000000</v>
+      </c>
+      <c r="G13" s="6">
+        <v>134511000000000</v>
+      </c>
+      <c r="H13" s="6">
+        <v>134511000000000</v>
+      </c>
+      <c r="I13" s="6">
+        <v>134511000000000</v>
+      </c>
+      <c r="J13" s="6">
+        <v>134511000000000</v>
+      </c>
+      <c r="K13" s="6">
+        <v>134511000000000</v>
+      </c>
+      <c r="L13" s="6">
+        <v>134511000000000</v>
+      </c>
+      <c r="M13" s="6">
+        <v>134511000000000</v>
+      </c>
+      <c r="N13" s="6">
+        <v>134511000000000</v>
+      </c>
+      <c r="O13" s="6">
+        <v>134511000000000</v>
+      </c>
+      <c r="P13" s="6">
+        <v>134511000000000</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>134511000000000</v>
+      </c>
+      <c r="R13" s="6">
+        <v>134511000000000</v>
+      </c>
+      <c r="S13" s="6">
+        <v>134511000000000</v>
+      </c>
+      <c r="T13" s="6">
+        <v>134511000000000</v>
+      </c>
+      <c r="U13" s="6">
+        <v>134511000000000</v>
+      </c>
+      <c r="V13" s="6">
+        <v>134511000000000</v>
+      </c>
+      <c r="W13" s="6">
+        <v>134511000000000</v>
+      </c>
+      <c r="X13" s="6">
+        <v>134511000000000</v>
+      </c>
+      <c r="Y13" s="6">
+        <v>134511000000000</v>
+      </c>
+      <c r="Z13" s="6">
+        <v>134511000000000</v>
+      </c>
+      <c r="AA13" s="6">
+        <v>134511000000000</v>
+      </c>
+      <c r="AB13" s="6">
+        <v>134511000000000</v>
+      </c>
+      <c r="AC13" s="6">
+        <v>134511000000000</v>
       </c>
     </row>
   </sheetData>
@@ -1133,7 +1717,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
@@ -1243,22 +1827,22 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="5">
-        <v>0</v>
-      </c>
-      <c r="C2" s="5">
+      <c r="B2" s="8">
+        <v>0</v>
+      </c>
+      <c r="C2" s="8">
         <f t="shared" ref="C2:AE2" si="0">$B2</f>
         <v>0</v>
       </c>
-      <c r="D2" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E2" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F2" s="5">
+      <c r="D2" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E2" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F2" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1367,144 +1951,139 @@
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="5">
-        <f>Evolved!B14</f>
+      <c r="B3" s="8">
         <v>1</v>
       </c>
-      <c r="C3" s="5">
-        <f>Evolved!C14</f>
+      <c r="C3" s="8">
         <v>1</v>
       </c>
-      <c r="D3" s="5">
-        <f>Evolved!D14</f>
+      <c r="D3" s="8">
         <v>1</v>
       </c>
-      <c r="E3" s="5">
-        <f>Evolved!E14</f>
+      <c r="E3" s="8">
         <v>1</v>
       </c>
-      <c r="F3" s="5">
-        <f>Evolved!F14</f>
+      <c r="F3" s="8">
         <v>1</v>
       </c>
       <c r="G3" s="5">
-        <f>Evolved!G14</f>
-        <v>0.95799331103678753</v>
+        <f>1-SUM(G7:G8)</f>
+        <v>0.94523727313859496</v>
       </c>
       <c r="H3" s="5">
-        <f>Evolved!H14</f>
-        <v>0.91598662207357506</v>
+        <f t="shared" ref="H3:AE3" si="1">1-SUM(H7:H8)</f>
+        <v>0.89047454627718992</v>
       </c>
       <c r="I3" s="5">
-        <f>Evolved!I14</f>
-        <v>0.87397993311037681</v>
+        <f t="shared" si="1"/>
+        <v>0.83571181941578487</v>
       </c>
       <c r="J3" s="5">
-        <f>Evolved!J14</f>
-        <v>0.83197324414716434</v>
+        <f t="shared" si="1"/>
+        <v>0.78094909255437983</v>
       </c>
       <c r="K3" s="5">
-        <f>Evolved!K14</f>
-        <v>0.78996655518395187</v>
+        <f t="shared" si="1"/>
+        <v>0.72618636569297479</v>
       </c>
       <c r="L3" s="5">
-        <f>Evolved!L14</f>
-        <v>0.711973244147174</v>
+        <f t="shared" si="1"/>
+        <v>0.72618636569297479</v>
       </c>
       <c r="M3" s="5">
-        <f>Evolved!M14</f>
-        <v>0.63397993311036771</v>
+        <f t="shared" si="1"/>
+        <v>0.72618636569297479</v>
       </c>
       <c r="N3" s="5">
-        <f>Evolved!N14</f>
-        <v>0.55598662207358984</v>
+        <f t="shared" si="1"/>
+        <v>0.72618636569297479</v>
       </c>
       <c r="O3" s="5">
-        <f>Evolved!O14</f>
-        <v>0.47799331103681197</v>
+        <f t="shared" si="1"/>
+        <v>0.72618636569297479</v>
       </c>
       <c r="P3" s="5">
-        <f>Evolved!P14</f>
-        <v>0.40000000000000568</v>
+        <f t="shared" si="1"/>
+        <v>0.72618636569297479</v>
       </c>
       <c r="Q3" s="5">
-        <f>Evolved!Q14</f>
-        <v>0.40000000000000568</v>
+        <f t="shared" si="1"/>
+        <v>0.72618636569297479</v>
       </c>
       <c r="R3" s="5">
-        <f>Evolved!R14</f>
-        <v>0.40000000000000568</v>
+        <f t="shared" si="1"/>
+        <v>0.72618636569297479</v>
       </c>
       <c r="S3" s="5">
-        <f>Evolved!S14</f>
-        <v>0.40000000000000568</v>
+        <f t="shared" si="1"/>
+        <v>0.72618636569297479</v>
       </c>
       <c r="T3" s="5">
-        <f>Evolved!T14</f>
-        <v>0.40000000000000568</v>
+        <f t="shared" si="1"/>
+        <v>0.72618636569297479</v>
       </c>
       <c r="U3" s="5">
-        <f>Evolved!U14</f>
-        <v>0.40000000000000568</v>
+        <f t="shared" si="1"/>
+        <v>0.72618636569297479</v>
       </c>
       <c r="V3" s="5">
-        <f>Evolved!V14</f>
-        <v>0.40000000000000568</v>
+        <f t="shared" si="1"/>
+        <v>0.72618636569297479</v>
       </c>
       <c r="W3" s="5">
-        <f>Evolved!W14</f>
-        <v>0.40000000000000568</v>
+        <f t="shared" si="1"/>
+        <v>0.72618636569297479</v>
       </c>
       <c r="X3" s="5">
-        <f>Evolved!X14</f>
-        <v>0.40000000000000568</v>
+        <f t="shared" si="1"/>
+        <v>0.72618636569297479</v>
       </c>
       <c r="Y3" s="5">
-        <f>Evolved!Y14</f>
-        <v>0.40000000000000568</v>
+        <f t="shared" si="1"/>
+        <v>0.72618636569297479</v>
       </c>
       <c r="Z3" s="5">
-        <f>Evolved!Z14</f>
-        <v>0.40000000000000568</v>
+        <f t="shared" si="1"/>
+        <v>0.72618636569297479</v>
       </c>
       <c r="AA3" s="5">
-        <f>Evolved!AA14</f>
-        <v>0.40000000000000568</v>
+        <f t="shared" si="1"/>
+        <v>0.72618636569297479</v>
       </c>
       <c r="AB3" s="5">
-        <f>Evolved!AB14</f>
-        <v>0.40000000000000568</v>
+        <f t="shared" si="1"/>
+        <v>0.72618636569297479</v>
       </c>
       <c r="AC3" s="5">
-        <f>Evolved!AC14</f>
-        <v>0.40000000000000568</v>
+        <f t="shared" si="1"/>
+        <v>0.72618636569297479</v>
       </c>
       <c r="AD3" s="5">
-        <f>Evolved!AD14</f>
-        <v>0.40000000000000568</v>
+        <f t="shared" si="1"/>
+        <v>0.72618636569297479</v>
       </c>
       <c r="AE3" s="5">
-        <f>Evolved!AE14</f>
-        <v>0.40000000000000568</v>
+        <f t="shared" si="1"/>
+        <v>0.72618636569297479</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="5">
-        <v>0</v>
-      </c>
-      <c r="C4" s="5">
-        <v>0</v>
-      </c>
-      <c r="D4" s="5">
-        <v>0</v>
-      </c>
-      <c r="E4" s="5">
-        <v>0</v>
-      </c>
-      <c r="F4" s="5">
+      <c r="B4" s="8">
+        <v>0</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0</v>
+      </c>
+      <c r="E4" s="8">
+        <v>0</v>
+      </c>
+      <c r="F4" s="8">
         <v>0</v>
       </c>
       <c r="G4" s="5">
@@ -1587,19 +2166,19 @@
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="5">
-        <v>0</v>
-      </c>
-      <c r="C5" s="5">
-        <v>0</v>
-      </c>
-      <c r="D5" s="5">
-        <v>0</v>
-      </c>
-      <c r="E5" s="5">
-        <v>0</v>
-      </c>
-      <c r="F5" s="5">
+      <c r="B5" s="8">
+        <v>0</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0</v>
+      </c>
+      <c r="E5" s="8">
+        <v>0</v>
+      </c>
+      <c r="F5" s="8">
         <v>0</v>
       </c>
       <c r="G5" s="5">
@@ -1682,19 +2261,19 @@
       <c r="A6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="5">
-        <v>0</v>
-      </c>
-      <c r="C6" s="5">
-        <v>0</v>
-      </c>
-      <c r="D6" s="5">
-        <v>0</v>
-      </c>
-      <c r="E6" s="5">
-        <v>0</v>
-      </c>
-      <c r="F6" s="5">
+      <c r="B6" s="8">
+        <v>0</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0</v>
+      </c>
+      <c r="E6" s="8">
+        <v>0</v>
+      </c>
+      <c r="F6" s="8">
         <v>0</v>
       </c>
       <c r="G6" s="5">
@@ -1777,250 +2356,240 @@
       <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="5">
-        <f>Evolved!B12</f>
-        <v>0</v>
-      </c>
-      <c r="C7" s="5">
-        <f>Evolved!C12</f>
-        <v>0</v>
-      </c>
-      <c r="D7" s="5">
-        <f>Evolved!D12</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="5">
-        <f>Evolved!E12</f>
-        <v>0</v>
-      </c>
-      <c r="F7" s="5">
-        <f>Evolved!F12</f>
-        <v>0</v>
-      </c>
-      <c r="G7" s="5">
-        <f>Evolved!G12</f>
-        <v>3.3846153846155858E-2</v>
-      </c>
-      <c r="H7" s="5">
-        <f>Evolved!H12</f>
-        <v>6.7692307692311715E-2</v>
-      </c>
-      <c r="I7" s="5">
-        <f>Evolved!I12</f>
-        <v>0.10153846153846757</v>
-      </c>
-      <c r="J7" s="5">
-        <f>Evolved!J12</f>
-        <v>0.13538461538462343</v>
-      </c>
-      <c r="K7" s="5">
-        <f>Evolved!K12</f>
-        <v>0.16923076923077929</v>
+      <c r="B7" s="8">
+        <v>0</v>
+      </c>
+      <c r="C7" s="8">
+        <v>0</v>
+      </c>
+      <c r="D7" s="8">
+        <v>0</v>
+      </c>
+      <c r="E7" s="8">
+        <v>0</v>
+      </c>
+      <c r="F7" s="8">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5" cm="1">
+        <f t="array" ref="G7">TREND(BNEF!$M16:$N16,BNEF!$M$14:$N$14,BHPSbP!G$1)</f>
+        <v>1.3363660912595776E-2</v>
+      </c>
+      <c r="H7" s="5" cm="1">
+        <f t="array" ref="H7">TREND(BNEF!$M16:$N16,BNEF!$M$14:$N$14,BHPSbP!H$1)</f>
+        <v>2.6727321825191552E-2</v>
+      </c>
+      <c r="I7" s="5" cm="1">
+        <f t="array" ref="I7">TREND(BNEF!$M16:$N16,BNEF!$M$14:$N$14,BHPSbP!I$1)</f>
+        <v>4.0090982737787328E-2</v>
+      </c>
+      <c r="J7" s="5" cm="1">
+        <f t="array" ref="J7">TREND(BNEF!$M16:$N16,BNEF!$M$14:$N$14,BHPSbP!J$1)</f>
+        <v>5.3454643650383105E-2</v>
+      </c>
+      <c r="K7" s="5" cm="1">
+        <f t="array" ref="K7">TREND(BNEF!$M16:$N16,BNEF!$M$14:$N$14,BHPSbP!K$1)</f>
+        <v>6.6818304562978881E-2</v>
       </c>
       <c r="L7" s="5">
-        <f>Evolved!L12</f>
-        <v>0.25031419284943013</v>
+        <f>K7</f>
+        <v>6.6818304562978881E-2</v>
       </c>
       <c r="M7" s="5">
-        <f>Evolved!M12</f>
-        <v>0.33139761646805255</v>
+        <f t="shared" ref="M7:AE7" si="2">L7</f>
+        <v>6.6818304562978881E-2</v>
       </c>
       <c r="N7" s="5">
-        <f>Evolved!N12</f>
-        <v>0.41248104008667497</v>
+        <f t="shared" si="2"/>
+        <v>6.6818304562978881E-2</v>
       </c>
       <c r="O7" s="5">
-        <f>Evolved!O12</f>
-        <v>0.49356446370532581</v>
+        <f t="shared" si="2"/>
+        <v>6.6818304562978881E-2</v>
       </c>
       <c r="P7" s="5">
-        <f>Evolved!P12</f>
-        <v>0.57464788732394823</v>
+        <f t="shared" si="2"/>
+        <v>6.6818304562978881E-2</v>
       </c>
       <c r="Q7" s="5">
-        <f>Evolved!Q12</f>
-        <v>0.57464788732394823</v>
+        <f t="shared" si="2"/>
+        <v>6.6818304562978881E-2</v>
       </c>
       <c r="R7" s="5">
-        <f>Evolved!R12</f>
-        <v>0.57464788732394823</v>
+        <f t="shared" si="2"/>
+        <v>6.6818304562978881E-2</v>
       </c>
       <c r="S7" s="5">
-        <f>Evolved!S12</f>
-        <v>0.57464788732394823</v>
+        <f t="shared" si="2"/>
+        <v>6.6818304562978881E-2</v>
       </c>
       <c r="T7" s="5">
-        <f>Evolved!T12</f>
-        <v>0.57464788732394823</v>
+        <f t="shared" si="2"/>
+        <v>6.6818304562978881E-2</v>
       </c>
       <c r="U7" s="5">
-        <f>Evolved!U12</f>
-        <v>0.57464788732394823</v>
+        <f t="shared" si="2"/>
+        <v>6.6818304562978881E-2</v>
       </c>
       <c r="V7" s="5">
-        <f>Evolved!V12</f>
-        <v>0.57464788732394823</v>
+        <f t="shared" si="2"/>
+        <v>6.6818304562978881E-2</v>
       </c>
       <c r="W7" s="5">
-        <f>Evolved!W12</f>
-        <v>0.57464788732394823</v>
+        <f t="shared" si="2"/>
+        <v>6.6818304562978881E-2</v>
       </c>
       <c r="X7" s="5">
-        <f>Evolved!X12</f>
-        <v>0.57464788732394823</v>
+        <f t="shared" si="2"/>
+        <v>6.6818304562978881E-2</v>
       </c>
       <c r="Y7" s="5">
-        <f>Evolved!Y12</f>
-        <v>0.57464788732394823</v>
+        <f t="shared" si="2"/>
+        <v>6.6818304562978881E-2</v>
       </c>
       <c r="Z7" s="5">
-        <f>Evolved!Z12</f>
-        <v>0.57464788732394823</v>
+        <f t="shared" si="2"/>
+        <v>6.6818304562978881E-2</v>
       </c>
       <c r="AA7" s="5">
-        <f>Evolved!AA12</f>
-        <v>0.57464788732394823</v>
+        <f t="shared" si="2"/>
+        <v>6.6818304562978881E-2</v>
       </c>
       <c r="AB7" s="5">
-        <f>Evolved!AB12</f>
-        <v>0.57464788732394823</v>
+        <f t="shared" si="2"/>
+        <v>6.6818304562978881E-2</v>
       </c>
       <c r="AC7" s="5">
-        <f>Evolved!AC12</f>
-        <v>0.57464788732394823</v>
+        <f t="shared" si="2"/>
+        <v>6.6818304562978881E-2</v>
       </c>
       <c r="AD7" s="5">
-        <f>Evolved!AD12</f>
-        <v>0.57464788732394823</v>
+        <f t="shared" si="2"/>
+        <v>6.6818304562978881E-2</v>
       </c>
       <c r="AE7" s="5">
-        <f>Evolved!AE12</f>
-        <v>0.57464788732394823</v>
+        <f t="shared" si="2"/>
+        <v>6.6818304562978881E-2</v>
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="5">
-        <f>Evolved!B13</f>
-        <v>0</v>
-      </c>
-      <c r="C8" s="5">
-        <f>Evolved!C13</f>
-        <v>0</v>
-      </c>
-      <c r="D8" s="5">
-        <f>Evolved!D13</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="5">
-        <f>Evolved!E13</f>
-        <v>0</v>
-      </c>
-      <c r="F8" s="5">
-        <f>Evolved!F13</f>
-        <v>0</v>
-      </c>
-      <c r="G8" s="5">
-        <f>Evolved!G13</f>
-        <v>8.1605351170566109E-3</v>
-      </c>
-      <c r="H8" s="5">
-        <f>Evolved!H13</f>
-        <v>1.6321070234113222E-2</v>
-      </c>
-      <c r="I8" s="5">
-        <f>Evolved!I13</f>
-        <v>2.4481605351169833E-2</v>
-      </c>
-      <c r="J8" s="5">
-        <f>Evolved!J13</f>
-        <v>3.2642140468226444E-2</v>
-      </c>
-      <c r="K8" s="5">
-        <f>Evolved!K13</f>
-        <v>4.0802675585283055E-2</v>
+      <c r="B8" s="8">
+        <v>0</v>
+      </c>
+      <c r="C8" s="8">
+        <v>0</v>
+      </c>
+      <c r="D8" s="8">
+        <v>0</v>
+      </c>
+      <c r="E8" s="8">
+        <v>0</v>
+      </c>
+      <c r="F8" s="8">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5" cm="1">
+        <f t="array" ref="G8">TREND(BNEF!$M15:$N15,BNEF!$M$14:$N$14,BHPSbP!G$1)</f>
+        <v>4.1399065948809266E-2</v>
+      </c>
+      <c r="H8" s="5" cm="1">
+        <f t="array" ref="H8">TREND(BNEF!$M15:$N15,BNEF!$M$14:$N$14,BHPSbP!H$1)</f>
+        <v>8.2798131897618532E-2</v>
+      </c>
+      <c r="I8" s="5" cm="1">
+        <f t="array" ref="I8">TREND(BNEF!$M15:$N15,BNEF!$M$14:$N$14,BHPSbP!I$1)</f>
+        <v>0.1241971978464278</v>
+      </c>
+      <c r="J8" s="5" cm="1">
+        <f t="array" ref="J8">TREND(BNEF!$M15:$N15,BNEF!$M$14:$N$14,BHPSbP!J$1)</f>
+        <v>0.16559626379523706</v>
+      </c>
+      <c r="K8" s="5" cm="1">
+        <f t="array" ref="K8">TREND(BNEF!$M15:$N15,BNEF!$M$14:$N$14,BHPSbP!K$1)</f>
+        <v>0.20699532974404633</v>
       </c>
       <c r="L8" s="5">
-        <f>Evolved!L13</f>
-        <v>3.7712563003438504E-2</v>
+        <f>K8</f>
+        <v>0.20699532974404633</v>
       </c>
       <c r="M8" s="5">
-        <f>Evolved!M13</f>
-        <v>3.4622450421593065E-2</v>
+        <f t="shared" ref="M8:AE8" si="3">L8</f>
+        <v>0.20699532974404633</v>
       </c>
       <c r="N8" s="5">
-        <f>Evolved!N13</f>
-        <v>3.1532337839747626E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.20699532974404633</v>
       </c>
       <c r="O8" s="5">
-        <f>Evolved!O13</f>
-        <v>2.8442225257901299E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.20699532974404633</v>
       </c>
       <c r="P8" s="5">
-        <f>Evolved!P13</f>
-        <v>2.535211267605586E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.20699532974404633</v>
       </c>
       <c r="Q8" s="5">
-        <f>Evolved!Q13</f>
-        <v>2.535211267605586E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.20699532974404633</v>
       </c>
       <c r="R8" s="5">
-        <f>Evolved!R13</f>
-        <v>2.535211267605586E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.20699532974404633</v>
       </c>
       <c r="S8" s="5">
-        <f>Evolved!S13</f>
-        <v>2.535211267605586E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.20699532974404633</v>
       </c>
       <c r="T8" s="5">
-        <f>Evolved!T13</f>
-        <v>2.535211267605586E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.20699532974404633</v>
       </c>
       <c r="U8" s="5">
-        <f>Evolved!U13</f>
-        <v>2.535211267605586E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.20699532974404633</v>
       </c>
       <c r="V8" s="5">
-        <f>Evolved!V13</f>
-        <v>2.535211267605586E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.20699532974404633</v>
       </c>
       <c r="W8" s="5">
-        <f>Evolved!W13</f>
-        <v>2.535211267605586E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.20699532974404633</v>
       </c>
       <c r="X8" s="5">
-        <f>Evolved!X13</f>
-        <v>2.535211267605586E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.20699532974404633</v>
       </c>
       <c r="Y8" s="5">
-        <f>Evolved!Y13</f>
-        <v>2.535211267605586E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.20699532974404633</v>
       </c>
       <c r="Z8" s="5">
-        <f>Evolved!Z13</f>
-        <v>2.535211267605586E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.20699532974404633</v>
       </c>
       <c r="AA8" s="5">
-        <f>Evolved!AA13</f>
-        <v>2.535211267605586E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.20699532974404633</v>
       </c>
       <c r="AB8" s="5">
-        <f>Evolved!AB13</f>
-        <v>2.535211267605586E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.20699532974404633</v>
       </c>
       <c r="AC8" s="5">
-        <f>Evolved!AC13</f>
-        <v>2.535211267605586E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.20699532974404633</v>
       </c>
       <c r="AD8" s="5">
-        <f>Evolved!AD13</f>
-        <v>2.535211267605586E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.20699532974404633</v>
       </c>
       <c r="AE8" s="5">
-        <f>Evolved!AE13</f>
-        <v>2.535211267605586E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.20699532974404633</v>
       </c>
     </row>
   </sheetData>

--- a/InputData/hydgn/BHPSbP/BAU Hydrogen Production Shr by Pathway.xlsx
+++ b/InputData/hydgn/BHPSbP/BAU Hydrogen Production Shr by Pathway.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\hydgn\BHPSbP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0746773-3F94-4C80-9392-DDC2F80141A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C64BE0A-0A22-4081-AE98-1D3A0E06D094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="1520" windowWidth="14400" windowHeight="9340" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="38">
   <si>
     <t>BHPSbP BAU Hydrogen Production Shares by Pathway</t>
   </si>
@@ -157,6 +157,24 @@
   </si>
   <si>
     <t>pgs. 10, 16</t>
+  </si>
+  <si>
+    <t>blue share of clean H2 supply</t>
+  </si>
+  <si>
+    <t>Hydrogen Supply Outlook Update: 10% Cut</t>
+  </si>
+  <si>
+    <t>https://www.bnef.com/insights/38875</t>
+  </si>
+  <si>
+    <t>Blue/green clean hydrogen split</t>
+  </si>
+  <si>
+    <t>Clean hydrogen offtake demand</t>
+  </si>
+  <si>
+    <t>Aggregated expected production from projects; included with permission</t>
   </si>
 </sst>
 </file>
@@ -166,7 +184,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -190,8 +208,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -201,6 +226,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -214,11 +245,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -232,10 +264,14 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -261,16 +297,16 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>536696</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>70110</xdr:rowOff>
+      <xdr:colOff>534092</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>171193</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
+        <xdr:cNvPr id="4" name="Picture 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8661492-DC81-408D-BF1C-FD0AB9692D4E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{150E1DB1-3649-4488-8F2D-F0C181554476}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -286,52 +322,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="609600" y="184150"/>
-          <a:ext cx="6023096" cy="3384810"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>534092</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>171193</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02F6FC29-38EA-45AA-81F7-E95FC535D07A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="606136" y="3752273"/>
-          <a:ext cx="5989320" cy="3360625"/>
+          <a:off x="606136" y="184006"/>
+          <a:ext cx="5989320" cy="3299289"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -606,10 +598,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.7265625" customWidth="1"/>
+    <col min="2" max="2" width="52.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -621,28 +614,63 @@
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B4" s="3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B5" s="3">
         <v>2025</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B5" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B6" s="4" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B7" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B7" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B8" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B10" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B12" s="3">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B15" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -653,25 +681,25 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FCF00DD-FBB5-4F2F-A64F-4218B001AAAE}">
-  <dimension ref="L3:O16"/>
+  <dimension ref="B3:AM35"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="3" spans="12:15" x14ac:dyDescent="0.35">
       <c r="M3" t="s">
         <v>10</v>
       </c>
-      <c r="N3">
-        <f>11.71/15.49</f>
-        <v>0.75597159457714658</v>
+      <c r="N3" s="11">
+        <f>B23</f>
+        <v>0.92344863824651802</v>
       </c>
     </row>
     <row r="4" spans="12:15" x14ac:dyDescent="0.35">
       <c r="M4" t="s">
         <v>11</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="9">
         <f>1-N3</f>
-        <v>0.24402840542285342</v>
+        <v>7.6551361753481983E-2</v>
       </c>
     </row>
     <row r="6" spans="12:15" x14ac:dyDescent="0.35">
@@ -703,7 +731,7 @@
       </c>
       <c r="N10" s="5">
         <f>N6/N8*N3</f>
-        <v>0.20699532974404683</v>
+        <v>0.25285282773415407</v>
       </c>
     </row>
     <row r="11" spans="12:15" x14ac:dyDescent="0.35">
@@ -712,7 +740,7 @@
       </c>
       <c r="N11" s="5">
         <f>N6/N8*N4</f>
-        <v>6.6818304562980088E-2</v>
+        <v>2.0960806572872845E-2</v>
       </c>
     </row>
     <row r="12" spans="12:15" x14ac:dyDescent="0.35">
@@ -737,7 +765,7 @@
       </c>
       <c r="N15" s="5">
         <f>N10</f>
-        <v>0.20699532974404683</v>
+        <v>0.25285282773415407</v>
       </c>
     </row>
     <row r="16" spans="12:15" x14ac:dyDescent="0.35">
@@ -749,8 +777,103 @@
       </c>
       <c r="N16" s="5">
         <f>N11</f>
-        <v>6.6818304562980088E-2</v>
-      </c>
+        <v>2.0960806572872845E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:39" x14ac:dyDescent="0.35">
+      <c r="B22" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="2:39" x14ac:dyDescent="0.35">
+      <c r="B23" s="9">
+        <v>0.92344863824651802</v>
+      </c>
+      <c r="C23" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" spans="2:39" x14ac:dyDescent="0.35">
+      <c r="N24" s="6"/>
+      <c r="O24" s="6"/>
+      <c r="P24" s="6"/>
+      <c r="Q24" s="6"/>
+      <c r="R24" s="6"/>
+      <c r="S24" s="6"/>
+      <c r="T24" s="6"/>
+      <c r="U24" s="6"/>
+      <c r="V24" s="6"/>
+      <c r="W24" s="6"/>
+      <c r="X24" s="6"/>
+      <c r="Y24" s="6"/>
+      <c r="Z24" s="6"/>
+      <c r="AA24" s="6"/>
+      <c r="AB24" s="6"/>
+      <c r="AC24" s="6"/>
+      <c r="AD24" s="6"/>
+      <c r="AE24" s="6"/>
+      <c r="AF24" s="6"/>
+      <c r="AG24" s="6"/>
+      <c r="AH24" s="6"/>
+      <c r="AI24" s="6"/>
+      <c r="AJ24" s="6"/>
+      <c r="AK24" s="6"/>
+      <c r="AL24" s="6"/>
+      <c r="AM24" s="6"/>
+    </row>
+    <row r="28" spans="2:39" x14ac:dyDescent="0.35">
+      <c r="N28" s="6"/>
+      <c r="O28" s="6"/>
+      <c r="P28" s="6"/>
+      <c r="Q28" s="6"/>
+      <c r="R28" s="6"/>
+      <c r="S28" s="6"/>
+      <c r="T28" s="6"/>
+      <c r="U28" s="6"/>
+      <c r="V28" s="6"/>
+      <c r="W28" s="6"/>
+      <c r="X28" s="6"/>
+      <c r="Y28" s="6"/>
+      <c r="Z28" s="6"/>
+      <c r="AA28" s="6"/>
+      <c r="AB28" s="6"/>
+      <c r="AC28" s="6"/>
+      <c r="AD28" s="6"/>
+      <c r="AE28" s="6"/>
+      <c r="AF28" s="6"/>
+      <c r="AG28" s="6"/>
+      <c r="AH28" s="6"/>
+      <c r="AI28" s="6"/>
+      <c r="AJ28" s="6"/>
+      <c r="AK28" s="6"/>
+      <c r="AL28" s="6"/>
+      <c r="AM28" s="6"/>
+    </row>
+    <row r="32" spans="2:39" x14ac:dyDescent="0.35">
+      <c r="N32" s="6"/>
+      <c r="O32" s="6"/>
+      <c r="P32" s="6"/>
+      <c r="Q32" s="6"/>
+      <c r="R32" s="6"/>
+      <c r="S32" s="6"/>
+    </row>
+    <row r="34" spans="14:20" x14ac:dyDescent="0.35">
+      <c r="N34" s="9"/>
+      <c r="O34" s="9"/>
+      <c r="P34" s="9"/>
+      <c r="Q34" s="9"/>
+      <c r="R34" s="9"/>
+      <c r="S34" s="9"/>
+      <c r="T34" s="6"/>
+    </row>
+    <row r="35" spans="14:20" x14ac:dyDescent="0.35">
+      <c r="N35" s="9"/>
+      <c r="O35" s="9"/>
+      <c r="P35" s="9"/>
+      <c r="Q35" s="9"/>
+      <c r="R35" s="9"/>
+      <c r="S35" s="9"/>
+      <c r="T35" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1968,103 +2091,103 @@
       </c>
       <c r="G3" s="5">
         <f>1-SUM(G7:G8)</f>
-        <v>0.94523727313859496</v>
+        <v>0.94523727313858963</v>
       </c>
       <c r="H3" s="5">
         <f t="shared" ref="H3:AE3" si="1">1-SUM(H7:H8)</f>
-        <v>0.89047454627718992</v>
+        <v>0.89047454627718103</v>
       </c>
       <c r="I3" s="5">
         <f t="shared" si="1"/>
-        <v>0.83571181941578487</v>
+        <v>0.83571181941578665</v>
       </c>
       <c r="J3" s="5">
         <f t="shared" si="1"/>
-        <v>0.78094909255437983</v>
+        <v>0.78094909255437628</v>
       </c>
       <c r="K3" s="5">
         <f t="shared" si="1"/>
-        <v>0.72618636569297479</v>
+        <v>0.72618636569296768</v>
       </c>
       <c r="L3" s="5">
         <f t="shared" si="1"/>
-        <v>0.72618636569297479</v>
+        <v>0.72618636569296768</v>
       </c>
       <c r="M3" s="5">
         <f t="shared" si="1"/>
-        <v>0.72618636569297479</v>
+        <v>0.72618636569296768</v>
       </c>
       <c r="N3" s="5">
         <f t="shared" si="1"/>
-        <v>0.72618636569297479</v>
+        <v>0.72618636569296768</v>
       </c>
       <c r="O3" s="5">
         <f t="shared" si="1"/>
-        <v>0.72618636569297479</v>
+        <v>0.72618636569296768</v>
       </c>
       <c r="P3" s="5">
         <f t="shared" si="1"/>
-        <v>0.72618636569297479</v>
+        <v>0.72618636569296768</v>
       </c>
       <c r="Q3" s="5">
         <f t="shared" si="1"/>
-        <v>0.72618636569297479</v>
+        <v>0.72618636569296768</v>
       </c>
       <c r="R3" s="5">
         <f t="shared" si="1"/>
-        <v>0.72618636569297479</v>
+        <v>0.72618636569296768</v>
       </c>
       <c r="S3" s="5">
         <f t="shared" si="1"/>
-        <v>0.72618636569297479</v>
+        <v>0.72618636569296768</v>
       </c>
       <c r="T3" s="5">
         <f t="shared" si="1"/>
-        <v>0.72618636569297479</v>
+        <v>0.72618636569296768</v>
       </c>
       <c r="U3" s="5">
         <f t="shared" si="1"/>
-        <v>0.72618636569297479</v>
+        <v>0.72618636569296768</v>
       </c>
       <c r="V3" s="5">
         <f t="shared" si="1"/>
-        <v>0.72618636569297479</v>
+        <v>0.72618636569296768</v>
       </c>
       <c r="W3" s="5">
         <f t="shared" si="1"/>
-        <v>0.72618636569297479</v>
+        <v>0.72618636569296768</v>
       </c>
       <c r="X3" s="5">
         <f t="shared" si="1"/>
-        <v>0.72618636569297479</v>
+        <v>0.72618636569296768</v>
       </c>
       <c r="Y3" s="5">
         <f t="shared" si="1"/>
-        <v>0.72618636569297479</v>
+        <v>0.72618636569296768</v>
       </c>
       <c r="Z3" s="5">
         <f t="shared" si="1"/>
-        <v>0.72618636569297479</v>
+        <v>0.72618636569296768</v>
       </c>
       <c r="AA3" s="5">
         <f t="shared" si="1"/>
-        <v>0.72618636569297479</v>
+        <v>0.72618636569296768</v>
       </c>
       <c r="AB3" s="5">
         <f t="shared" si="1"/>
-        <v>0.72618636569297479</v>
+        <v>0.72618636569296768</v>
       </c>
       <c r="AC3" s="5">
         <f t="shared" si="1"/>
-        <v>0.72618636569297479</v>
+        <v>0.72618636569296768</v>
       </c>
       <c r="AD3" s="5">
         <f t="shared" si="1"/>
-        <v>0.72618636569297479</v>
+        <v>0.72618636569296768</v>
       </c>
       <c r="AE3" s="5">
         <f t="shared" si="1"/>
-        <v>0.72618636569297479</v>
+        <v>0.72618636569296768</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.35">
@@ -2373,103 +2496,103 @@
       </c>
       <c r="G7" s="5" cm="1">
         <f t="array" ref="G7">TREND(BNEF!$M16:$N16,BNEF!$M$14:$N$14,BHPSbP!G$1)</f>
-        <v>1.3363660912595776E-2</v>
+        <v>4.1921613145756709E-3</v>
       </c>
       <c r="H7" s="5" cm="1">
         <f t="array" ref="H7">TREND(BNEF!$M16:$N16,BNEF!$M$14:$N$14,BHPSbP!H$1)</f>
-        <v>2.6727321825191552E-2</v>
+        <v>8.3843226291495654E-3</v>
       </c>
       <c r="I7" s="5" cm="1">
         <f t="array" ref="I7">TREND(BNEF!$M16:$N16,BNEF!$M$14:$N$14,BHPSbP!I$1)</f>
-        <v>4.0090982737787328E-2</v>
+        <v>1.257648394372346E-2</v>
       </c>
       <c r="J7" s="5" cm="1">
         <f t="array" ref="J7">TREND(BNEF!$M16:$N16,BNEF!$M$14:$N$14,BHPSbP!J$1)</f>
-        <v>5.3454643650383105E-2</v>
+        <v>1.6768645258299131E-2</v>
       </c>
       <c r="K7" s="5" cm="1">
         <f t="array" ref="K7">TREND(BNEF!$M16:$N16,BNEF!$M$14:$N$14,BHPSbP!K$1)</f>
-        <v>6.6818304562978881E-2</v>
+        <v>2.0960806572873025E-2</v>
       </c>
       <c r="L7" s="5">
         <f>K7</f>
-        <v>6.6818304562978881E-2</v>
+        <v>2.0960806572873025E-2</v>
       </c>
       <c r="M7" s="5">
         <f t="shared" ref="M7:AE7" si="2">L7</f>
-        <v>6.6818304562978881E-2</v>
+        <v>2.0960806572873025E-2</v>
       </c>
       <c r="N7" s="5">
         <f t="shared" si="2"/>
-        <v>6.6818304562978881E-2</v>
+        <v>2.0960806572873025E-2</v>
       </c>
       <c r="O7" s="5">
         <f t="shared" si="2"/>
-        <v>6.6818304562978881E-2</v>
+        <v>2.0960806572873025E-2</v>
       </c>
       <c r="P7" s="5">
         <f t="shared" si="2"/>
-        <v>6.6818304562978881E-2</v>
+        <v>2.0960806572873025E-2</v>
       </c>
       <c r="Q7" s="5">
         <f t="shared" si="2"/>
-        <v>6.6818304562978881E-2</v>
+        <v>2.0960806572873025E-2</v>
       </c>
       <c r="R7" s="5">
         <f t="shared" si="2"/>
-        <v>6.6818304562978881E-2</v>
+        <v>2.0960806572873025E-2</v>
       </c>
       <c r="S7" s="5">
         <f t="shared" si="2"/>
-        <v>6.6818304562978881E-2</v>
+        <v>2.0960806572873025E-2</v>
       </c>
       <c r="T7" s="5">
         <f t="shared" si="2"/>
-        <v>6.6818304562978881E-2</v>
+        <v>2.0960806572873025E-2</v>
       </c>
       <c r="U7" s="5">
         <f t="shared" si="2"/>
-        <v>6.6818304562978881E-2</v>
+        <v>2.0960806572873025E-2</v>
       </c>
       <c r="V7" s="5">
         <f t="shared" si="2"/>
-        <v>6.6818304562978881E-2</v>
+        <v>2.0960806572873025E-2</v>
       </c>
       <c r="W7" s="5">
         <f t="shared" si="2"/>
-        <v>6.6818304562978881E-2</v>
+        <v>2.0960806572873025E-2</v>
       </c>
       <c r="X7" s="5">
         <f t="shared" si="2"/>
-        <v>6.6818304562978881E-2</v>
+        <v>2.0960806572873025E-2</v>
       </c>
       <c r="Y7" s="5">
         <f t="shared" si="2"/>
-        <v>6.6818304562978881E-2</v>
+        <v>2.0960806572873025E-2</v>
       </c>
       <c r="Z7" s="5">
         <f t="shared" si="2"/>
-        <v>6.6818304562978881E-2</v>
+        <v>2.0960806572873025E-2</v>
       </c>
       <c r="AA7" s="5">
         <f t="shared" si="2"/>
-        <v>6.6818304562978881E-2</v>
+        <v>2.0960806572873025E-2</v>
       </c>
       <c r="AB7" s="5">
         <f t="shared" si="2"/>
-        <v>6.6818304562978881E-2</v>
+        <v>2.0960806572873025E-2</v>
       </c>
       <c r="AC7" s="5">
         <f t="shared" si="2"/>
-        <v>6.6818304562978881E-2</v>
+        <v>2.0960806572873025E-2</v>
       </c>
       <c r="AD7" s="5">
         <f t="shared" si="2"/>
-        <v>6.6818304562978881E-2</v>
+        <v>2.0960806572873025E-2</v>
       </c>
       <c r="AE7" s="5">
         <f t="shared" si="2"/>
-        <v>6.6818304562978881E-2</v>
+        <v>2.0960806572873025E-2</v>
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.35">
@@ -2493,103 +2616,103 @@
       </c>
       <c r="G8" s="5" cm="1">
         <f t="array" ref="G8">TREND(BNEF!$M15:$N15,BNEF!$M$14:$N$14,BHPSbP!G$1)</f>
-        <v>4.1399065948809266E-2</v>
+        <v>5.05705655468347E-2</v>
       </c>
       <c r="H8" s="5" cm="1">
         <f t="array" ref="H8">TREND(BNEF!$M15:$N15,BNEF!$M$14:$N$14,BHPSbP!H$1)</f>
-        <v>8.2798131897618532E-2</v>
+        <v>0.1011411310936694</v>
       </c>
       <c r="I8" s="5" cm="1">
         <f t="array" ref="I8">TREND(BNEF!$M15:$N15,BNEF!$M$14:$N$14,BHPSbP!I$1)</f>
-        <v>0.1241971978464278</v>
+        <v>0.15171169664048989</v>
       </c>
       <c r="J8" s="5" cm="1">
         <f t="array" ref="J8">TREND(BNEF!$M15:$N15,BNEF!$M$14:$N$14,BHPSbP!J$1)</f>
-        <v>0.16559626379523706</v>
+        <v>0.20228226218732459</v>
       </c>
       <c r="K8" s="5" cm="1">
         <f t="array" ref="K8">TREND(BNEF!$M15:$N15,BNEF!$M$14:$N$14,BHPSbP!K$1)</f>
-        <v>0.20699532974404633</v>
+        <v>0.25285282773415929</v>
       </c>
       <c r="L8" s="5">
         <f>K8</f>
-        <v>0.20699532974404633</v>
+        <v>0.25285282773415929</v>
       </c>
       <c r="M8" s="5">
         <f t="shared" ref="M8:AE8" si="3">L8</f>
-        <v>0.20699532974404633</v>
+        <v>0.25285282773415929</v>
       </c>
       <c r="N8" s="5">
         <f t="shared" si="3"/>
-        <v>0.20699532974404633</v>
+        <v>0.25285282773415929</v>
       </c>
       <c r="O8" s="5">
         <f t="shared" si="3"/>
-        <v>0.20699532974404633</v>
+        <v>0.25285282773415929</v>
       </c>
       <c r="P8" s="5">
         <f t="shared" si="3"/>
-        <v>0.20699532974404633</v>
+        <v>0.25285282773415929</v>
       </c>
       <c r="Q8" s="5">
         <f t="shared" si="3"/>
-        <v>0.20699532974404633</v>
+        <v>0.25285282773415929</v>
       </c>
       <c r="R8" s="5">
         <f t="shared" si="3"/>
-        <v>0.20699532974404633</v>
+        <v>0.25285282773415929</v>
       </c>
       <c r="S8" s="5">
         <f t="shared" si="3"/>
-        <v>0.20699532974404633</v>
+        <v>0.25285282773415929</v>
       </c>
       <c r="T8" s="5">
         <f t="shared" si="3"/>
-        <v>0.20699532974404633</v>
+        <v>0.25285282773415929</v>
       </c>
       <c r="U8" s="5">
         <f t="shared" si="3"/>
-        <v>0.20699532974404633</v>
+        <v>0.25285282773415929</v>
       </c>
       <c r="V8" s="5">
         <f t="shared" si="3"/>
-        <v>0.20699532974404633</v>
+        <v>0.25285282773415929</v>
       </c>
       <c r="W8" s="5">
         <f t="shared" si="3"/>
-        <v>0.20699532974404633</v>
+        <v>0.25285282773415929</v>
       </c>
       <c r="X8" s="5">
         <f t="shared" si="3"/>
-        <v>0.20699532974404633</v>
+        <v>0.25285282773415929</v>
       </c>
       <c r="Y8" s="5">
         <f t="shared" si="3"/>
-        <v>0.20699532974404633</v>
+        <v>0.25285282773415929</v>
       </c>
       <c r="Z8" s="5">
         <f t="shared" si="3"/>
-        <v>0.20699532974404633</v>
+        <v>0.25285282773415929</v>
       </c>
       <c r="AA8" s="5">
         <f t="shared" si="3"/>
-        <v>0.20699532974404633</v>
+        <v>0.25285282773415929</v>
       </c>
       <c r="AB8" s="5">
         <f t="shared" si="3"/>
-        <v>0.20699532974404633</v>
+        <v>0.25285282773415929</v>
       </c>
       <c r="AC8" s="5">
         <f t="shared" si="3"/>
-        <v>0.20699532974404633</v>
+        <v>0.25285282773415929</v>
       </c>
       <c r="AD8" s="5">
         <f t="shared" si="3"/>
-        <v>0.20699532974404633</v>
+        <v>0.25285282773415929</v>
       </c>
       <c r="AE8" s="5">
         <f t="shared" si="3"/>
-        <v>0.20699532974404633</v>
+        <v>0.25285282773415929</v>
       </c>
     </row>
   </sheetData>

--- a/InputData/hydgn/BHPSbP/BAU Hydrogen Production Shr by Pathway.xlsx
+++ b/InputData/hydgn/BHPSbP/BAU Hydrogen Production Shr by Pathway.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\hydgn\BHPSbP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C64BE0A-0A22-4081-AE98-1D3A0E06D094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0746773-3F94-4C80-9392-DDC2F80141A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1520" yWindow="1520" windowWidth="14400" windowHeight="9340" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
   <si>
     <t>BHPSbP BAU Hydrogen Production Shares by Pathway</t>
   </si>
@@ -157,24 +157,6 @@
   </si>
   <si>
     <t>pgs. 10, 16</t>
-  </si>
-  <si>
-    <t>blue share of clean H2 supply</t>
-  </si>
-  <si>
-    <t>Hydrogen Supply Outlook Update: 10% Cut</t>
-  </si>
-  <si>
-    <t>https://www.bnef.com/insights/38875</t>
-  </si>
-  <si>
-    <t>Blue/green clean hydrogen split</t>
-  </si>
-  <si>
-    <t>Clean hydrogen offtake demand</t>
-  </si>
-  <si>
-    <t>Aggregated expected production from projects; included with permission</t>
   </si>
 </sst>
 </file>
@@ -184,7 +166,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -208,15 +190,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -226,12 +201,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -245,12 +214,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -264,14 +232,10 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -297,16 +261,16 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>534092</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>171193</xdr:rowOff>
+      <xdr:colOff>536696</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>70110</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{150E1DB1-3649-4488-8F2D-F0C181554476}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8661492-DC81-408D-BF1C-FD0AB9692D4E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -322,8 +286,52 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="606136" y="184006"/>
-          <a:ext cx="5989320" cy="3299289"/>
+          <a:off x="609600" y="184150"/>
+          <a:ext cx="6023096" cy="3384810"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>534092</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>171193</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02F6FC29-38EA-45AA-81F7-E95FC535D07A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="606136" y="3752273"/>
+          <a:ext cx="5989320" cy="3360625"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -598,11 +606,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.7265625" customWidth="1"/>
-    <col min="2" max="2" width="52.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -614,63 +621,28 @@
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>36</v>
+      <c r="B3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B4" t="s">
-        <v>28</v>
+      <c r="B4" s="3">
+        <v>2025</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B5" s="3">
-        <v>2025</v>
+      <c r="B5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B6" t="s">
-        <v>29</v>
+      <c r="B6" s="4" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B7" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B8" t="s">
+      <c r="B7" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B10" s="10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B12" s="3">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B13" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B14" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B15" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -681,25 +653,25 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FCF00DD-FBB5-4F2F-A64F-4218B001AAAE}">
-  <dimension ref="B3:AM35"/>
+  <dimension ref="L3:O16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="3" spans="12:15" x14ac:dyDescent="0.35">
       <c r="M3" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="11">
-        <f>B23</f>
-        <v>0.92344863824651802</v>
+      <c r="N3">
+        <f>11.71/15.49</f>
+        <v>0.75597159457714658</v>
       </c>
     </row>
     <row r="4" spans="12:15" x14ac:dyDescent="0.35">
       <c r="M4" t="s">
         <v>11</v>
       </c>
-      <c r="N4" s="9">
+      <c r="N4">
         <f>1-N3</f>
-        <v>7.6551361753481983E-2</v>
+        <v>0.24402840542285342</v>
       </c>
     </row>
     <row r="6" spans="12:15" x14ac:dyDescent="0.35">
@@ -731,7 +703,7 @@
       </c>
       <c r="N10" s="5">
         <f>N6/N8*N3</f>
-        <v>0.25285282773415407</v>
+        <v>0.20699532974404683</v>
       </c>
     </row>
     <row r="11" spans="12:15" x14ac:dyDescent="0.35">
@@ -740,7 +712,7 @@
       </c>
       <c r="N11" s="5">
         <f>N6/N8*N4</f>
-        <v>2.0960806572872845E-2</v>
+        <v>6.6818304562980088E-2</v>
       </c>
     </row>
     <row r="12" spans="12:15" x14ac:dyDescent="0.35">
@@ -765,7 +737,7 @@
       </c>
       <c r="N15" s="5">
         <f>N10</f>
-        <v>0.25285282773415407</v>
+        <v>0.20699532974404683</v>
       </c>
     </row>
     <row r="16" spans="12:15" x14ac:dyDescent="0.35">
@@ -777,103 +749,8 @@
       </c>
       <c r="N16" s="5">
         <f>N11</f>
-        <v>2.0960806572872845E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="2:39" x14ac:dyDescent="0.35">
-      <c r="B22" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="23" spans="2:39" x14ac:dyDescent="0.35">
-      <c r="B23" s="9">
-        <v>0.92344863824651802</v>
-      </c>
-      <c r="C23" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24" spans="2:39" x14ac:dyDescent="0.35">
-      <c r="N24" s="6"/>
-      <c r="O24" s="6"/>
-      <c r="P24" s="6"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="6"/>
-      <c r="S24" s="6"/>
-      <c r="T24" s="6"/>
-      <c r="U24" s="6"/>
-      <c r="V24" s="6"/>
-      <c r="W24" s="6"/>
-      <c r="X24" s="6"/>
-      <c r="Y24" s="6"/>
-      <c r="Z24" s="6"/>
-      <c r="AA24" s="6"/>
-      <c r="AB24" s="6"/>
-      <c r="AC24" s="6"/>
-      <c r="AD24" s="6"/>
-      <c r="AE24" s="6"/>
-      <c r="AF24" s="6"/>
-      <c r="AG24" s="6"/>
-      <c r="AH24" s="6"/>
-      <c r="AI24" s="6"/>
-      <c r="AJ24" s="6"/>
-      <c r="AK24" s="6"/>
-      <c r="AL24" s="6"/>
-      <c r="AM24" s="6"/>
-    </row>
-    <row r="28" spans="2:39" x14ac:dyDescent="0.35">
-      <c r="N28" s="6"/>
-      <c r="O28" s="6"/>
-      <c r="P28" s="6"/>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="6"/>
-      <c r="S28" s="6"/>
-      <c r="T28" s="6"/>
-      <c r="U28" s="6"/>
-      <c r="V28" s="6"/>
-      <c r="W28" s="6"/>
-      <c r="X28" s="6"/>
-      <c r="Y28" s="6"/>
-      <c r="Z28" s="6"/>
-      <c r="AA28" s="6"/>
-      <c r="AB28" s="6"/>
-      <c r="AC28" s="6"/>
-      <c r="AD28" s="6"/>
-      <c r="AE28" s="6"/>
-      <c r="AF28" s="6"/>
-      <c r="AG28" s="6"/>
-      <c r="AH28" s="6"/>
-      <c r="AI28" s="6"/>
-      <c r="AJ28" s="6"/>
-      <c r="AK28" s="6"/>
-      <c r="AL28" s="6"/>
-      <c r="AM28" s="6"/>
-    </row>
-    <row r="32" spans="2:39" x14ac:dyDescent="0.35">
-      <c r="N32" s="6"/>
-      <c r="O32" s="6"/>
-      <c r="P32" s="6"/>
-      <c r="Q32" s="6"/>
-      <c r="R32" s="6"/>
-      <c r="S32" s="6"/>
-    </row>
-    <row r="34" spans="14:20" x14ac:dyDescent="0.35">
-      <c r="N34" s="9"/>
-      <c r="O34" s="9"/>
-      <c r="P34" s="9"/>
-      <c r="Q34" s="9"/>
-      <c r="R34" s="9"/>
-      <c r="S34" s="9"/>
-      <c r="T34" s="6"/>
-    </row>
-    <row r="35" spans="14:20" x14ac:dyDescent="0.35">
-      <c r="N35" s="9"/>
-      <c r="O35" s="9"/>
-      <c r="P35" s="9"/>
-      <c r="Q35" s="9"/>
-      <c r="R35" s="9"/>
-      <c r="S35" s="9"/>
-      <c r="T35" s="6"/>
+        <v>6.6818304562980088E-2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2091,103 +1968,103 @@
       </c>
       <c r="G3" s="5">
         <f>1-SUM(G7:G8)</f>
-        <v>0.94523727313858963</v>
+        <v>0.94523727313859496</v>
       </c>
       <c r="H3" s="5">
         <f t="shared" ref="H3:AE3" si="1">1-SUM(H7:H8)</f>
-        <v>0.89047454627718103</v>
+        <v>0.89047454627718992</v>
       </c>
       <c r="I3" s="5">
         <f t="shared" si="1"/>
-        <v>0.83571181941578665</v>
+        <v>0.83571181941578487</v>
       </c>
       <c r="J3" s="5">
         <f t="shared" si="1"/>
-        <v>0.78094909255437628</v>
+        <v>0.78094909255437983</v>
       </c>
       <c r="K3" s="5">
         <f t="shared" si="1"/>
-        <v>0.72618636569296768</v>
+        <v>0.72618636569297479</v>
       </c>
       <c r="L3" s="5">
         <f t="shared" si="1"/>
-        <v>0.72618636569296768</v>
+        <v>0.72618636569297479</v>
       </c>
       <c r="M3" s="5">
         <f t="shared" si="1"/>
-        <v>0.72618636569296768</v>
+        <v>0.72618636569297479</v>
       </c>
       <c r="N3" s="5">
         <f t="shared" si="1"/>
-        <v>0.72618636569296768</v>
+        <v>0.72618636569297479</v>
       </c>
       <c r="O3" s="5">
         <f t="shared" si="1"/>
-        <v>0.72618636569296768</v>
+        <v>0.72618636569297479</v>
       </c>
       <c r="P3" s="5">
         <f t="shared" si="1"/>
-        <v>0.72618636569296768</v>
+        <v>0.72618636569297479</v>
       </c>
       <c r="Q3" s="5">
         <f t="shared" si="1"/>
-        <v>0.72618636569296768</v>
+        <v>0.72618636569297479</v>
       </c>
       <c r="R3" s="5">
         <f t="shared" si="1"/>
-        <v>0.72618636569296768</v>
+        <v>0.72618636569297479</v>
       </c>
       <c r="S3" s="5">
         <f t="shared" si="1"/>
-        <v>0.72618636569296768</v>
+        <v>0.72618636569297479</v>
       </c>
       <c r="T3" s="5">
         <f t="shared" si="1"/>
-        <v>0.72618636569296768</v>
+        <v>0.72618636569297479</v>
       </c>
       <c r="U3" s="5">
         <f t="shared" si="1"/>
-        <v>0.72618636569296768</v>
+        <v>0.72618636569297479</v>
       </c>
       <c r="V3" s="5">
         <f t="shared" si="1"/>
-        <v>0.72618636569296768</v>
+        <v>0.72618636569297479</v>
       </c>
       <c r="W3" s="5">
         <f t="shared" si="1"/>
-        <v>0.72618636569296768</v>
+        <v>0.72618636569297479</v>
       </c>
       <c r="X3" s="5">
         <f t="shared" si="1"/>
-        <v>0.72618636569296768</v>
+        <v>0.72618636569297479</v>
       </c>
       <c r="Y3" s="5">
         <f t="shared" si="1"/>
-        <v>0.72618636569296768</v>
+        <v>0.72618636569297479</v>
       </c>
       <c r="Z3" s="5">
         <f t="shared" si="1"/>
-        <v>0.72618636569296768</v>
+        <v>0.72618636569297479</v>
       </c>
       <c r="AA3" s="5">
         <f t="shared" si="1"/>
-        <v>0.72618636569296768</v>
+        <v>0.72618636569297479</v>
       </c>
       <c r="AB3" s="5">
         <f t="shared" si="1"/>
-        <v>0.72618636569296768</v>
+        <v>0.72618636569297479</v>
       </c>
       <c r="AC3" s="5">
         <f t="shared" si="1"/>
-        <v>0.72618636569296768</v>
+        <v>0.72618636569297479</v>
       </c>
       <c r="AD3" s="5">
         <f t="shared" si="1"/>
-        <v>0.72618636569296768</v>
+        <v>0.72618636569297479</v>
       </c>
       <c r="AE3" s="5">
         <f t="shared" si="1"/>
-        <v>0.72618636569296768</v>
+        <v>0.72618636569297479</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.35">
@@ -2496,103 +2373,103 @@
       </c>
       <c r="G7" s="5" cm="1">
         <f t="array" ref="G7">TREND(BNEF!$M16:$N16,BNEF!$M$14:$N$14,BHPSbP!G$1)</f>
-        <v>4.1921613145756709E-3</v>
+        <v>1.3363660912595776E-2</v>
       </c>
       <c r="H7" s="5" cm="1">
         <f t="array" ref="H7">TREND(BNEF!$M16:$N16,BNEF!$M$14:$N$14,BHPSbP!H$1)</f>
-        <v>8.3843226291495654E-3</v>
+        <v>2.6727321825191552E-2</v>
       </c>
       <c r="I7" s="5" cm="1">
         <f t="array" ref="I7">TREND(BNEF!$M16:$N16,BNEF!$M$14:$N$14,BHPSbP!I$1)</f>
-        <v>1.257648394372346E-2</v>
+        <v>4.0090982737787328E-2</v>
       </c>
       <c r="J7" s="5" cm="1">
         <f t="array" ref="J7">TREND(BNEF!$M16:$N16,BNEF!$M$14:$N$14,BHPSbP!J$1)</f>
-        <v>1.6768645258299131E-2</v>
+        <v>5.3454643650383105E-2</v>
       </c>
       <c r="K7" s="5" cm="1">
         <f t="array" ref="K7">TREND(BNEF!$M16:$N16,BNEF!$M$14:$N$14,BHPSbP!K$1)</f>
-        <v>2.0960806572873025E-2</v>
+        <v>6.6818304562978881E-2</v>
       </c>
       <c r="L7" s="5">
         <f>K7</f>
-        <v>2.0960806572873025E-2</v>
+        <v>6.6818304562978881E-2</v>
       </c>
       <c r="M7" s="5">
         <f t="shared" ref="M7:AE7" si="2">L7</f>
-        <v>2.0960806572873025E-2</v>
+        <v>6.6818304562978881E-2</v>
       </c>
       <c r="N7" s="5">
         <f t="shared" si="2"/>
-        <v>2.0960806572873025E-2</v>
+        <v>6.6818304562978881E-2</v>
       </c>
       <c r="O7" s="5">
         <f t="shared" si="2"/>
-        <v>2.0960806572873025E-2</v>
+        <v>6.6818304562978881E-2</v>
       </c>
       <c r="P7" s="5">
         <f t="shared" si="2"/>
-        <v>2.0960806572873025E-2</v>
+        <v>6.6818304562978881E-2</v>
       </c>
       <c r="Q7" s="5">
         <f t="shared" si="2"/>
-        <v>2.0960806572873025E-2</v>
+        <v>6.6818304562978881E-2</v>
       </c>
       <c r="R7" s="5">
         <f t="shared" si="2"/>
-        <v>2.0960806572873025E-2</v>
+        <v>6.6818304562978881E-2</v>
       </c>
       <c r="S7" s="5">
         <f t="shared" si="2"/>
-        <v>2.0960806572873025E-2</v>
+        <v>6.6818304562978881E-2</v>
       </c>
       <c r="T7" s="5">
         <f t="shared" si="2"/>
-        <v>2.0960806572873025E-2</v>
+        <v>6.6818304562978881E-2</v>
       </c>
       <c r="U7" s="5">
         <f t="shared" si="2"/>
-        <v>2.0960806572873025E-2</v>
+        <v>6.6818304562978881E-2</v>
       </c>
       <c r="V7" s="5">
         <f t="shared" si="2"/>
-        <v>2.0960806572873025E-2</v>
+        <v>6.6818304562978881E-2</v>
       </c>
       <c r="W7" s="5">
         <f t="shared" si="2"/>
-        <v>2.0960806572873025E-2</v>
+        <v>6.6818304562978881E-2</v>
       </c>
       <c r="X7" s="5">
         <f t="shared" si="2"/>
-        <v>2.0960806572873025E-2</v>
+        <v>6.6818304562978881E-2</v>
       </c>
       <c r="Y7" s="5">
         <f t="shared" si="2"/>
-        <v>2.0960806572873025E-2</v>
+        <v>6.6818304562978881E-2</v>
       </c>
       <c r="Z7" s="5">
         <f t="shared" si="2"/>
-        <v>2.0960806572873025E-2</v>
+        <v>6.6818304562978881E-2</v>
       </c>
       <c r="AA7" s="5">
         <f t="shared" si="2"/>
-        <v>2.0960806572873025E-2</v>
+        <v>6.6818304562978881E-2</v>
       </c>
       <c r="AB7" s="5">
         <f t="shared" si="2"/>
-        <v>2.0960806572873025E-2</v>
+        <v>6.6818304562978881E-2</v>
       </c>
       <c r="AC7" s="5">
         <f t="shared" si="2"/>
-        <v>2.0960806572873025E-2</v>
+        <v>6.6818304562978881E-2</v>
       </c>
       <c r="AD7" s="5">
         <f t="shared" si="2"/>
-        <v>2.0960806572873025E-2</v>
+        <v>6.6818304562978881E-2</v>
       </c>
       <c r="AE7" s="5">
         <f t="shared" si="2"/>
-        <v>2.0960806572873025E-2</v>
+        <v>6.6818304562978881E-2</v>
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.35">
@@ -2616,103 +2493,103 @@
       </c>
       <c r="G8" s="5" cm="1">
         <f t="array" ref="G8">TREND(BNEF!$M15:$N15,BNEF!$M$14:$N$14,BHPSbP!G$1)</f>
-        <v>5.05705655468347E-2</v>
+        <v>4.1399065948809266E-2</v>
       </c>
       <c r="H8" s="5" cm="1">
         <f t="array" ref="H8">TREND(BNEF!$M15:$N15,BNEF!$M$14:$N$14,BHPSbP!H$1)</f>
-        <v>0.1011411310936694</v>
+        <v>8.2798131897618532E-2</v>
       </c>
       <c r="I8" s="5" cm="1">
         <f t="array" ref="I8">TREND(BNEF!$M15:$N15,BNEF!$M$14:$N$14,BHPSbP!I$1)</f>
-        <v>0.15171169664048989</v>
+        <v>0.1241971978464278</v>
       </c>
       <c r="J8" s="5" cm="1">
         <f t="array" ref="J8">TREND(BNEF!$M15:$N15,BNEF!$M$14:$N$14,BHPSbP!J$1)</f>
-        <v>0.20228226218732459</v>
+        <v>0.16559626379523706</v>
       </c>
       <c r="K8" s="5" cm="1">
         <f t="array" ref="K8">TREND(BNEF!$M15:$N15,BNEF!$M$14:$N$14,BHPSbP!K$1)</f>
-        <v>0.25285282773415929</v>
+        <v>0.20699532974404633</v>
       </c>
       <c r="L8" s="5">
         <f>K8</f>
-        <v>0.25285282773415929</v>
+        <v>0.20699532974404633</v>
       </c>
       <c r="M8" s="5">
         <f t="shared" ref="M8:AE8" si="3">L8</f>
-        <v>0.25285282773415929</v>
+        <v>0.20699532974404633</v>
       </c>
       <c r="N8" s="5">
         <f t="shared" si="3"/>
-        <v>0.25285282773415929</v>
+        <v>0.20699532974404633</v>
       </c>
       <c r="O8" s="5">
         <f t="shared" si="3"/>
-        <v>0.25285282773415929</v>
+        <v>0.20699532974404633</v>
       </c>
       <c r="P8" s="5">
         <f t="shared" si="3"/>
-        <v>0.25285282773415929</v>
+        <v>0.20699532974404633</v>
       </c>
       <c r="Q8" s="5">
         <f t="shared" si="3"/>
-        <v>0.25285282773415929</v>
+        <v>0.20699532974404633</v>
       </c>
       <c r="R8" s="5">
         <f t="shared" si="3"/>
-        <v>0.25285282773415929</v>
+        <v>0.20699532974404633</v>
       </c>
       <c r="S8" s="5">
         <f t="shared" si="3"/>
-        <v>0.25285282773415929</v>
+        <v>0.20699532974404633</v>
       </c>
       <c r="T8" s="5">
         <f t="shared" si="3"/>
-        <v>0.25285282773415929</v>
+        <v>0.20699532974404633</v>
       </c>
       <c r="U8" s="5">
         <f t="shared" si="3"/>
-        <v>0.25285282773415929</v>
+        <v>0.20699532974404633</v>
       </c>
       <c r="V8" s="5">
         <f t="shared" si="3"/>
-        <v>0.25285282773415929</v>
+        <v>0.20699532974404633</v>
       </c>
       <c r="W8" s="5">
         <f t="shared" si="3"/>
-        <v>0.25285282773415929</v>
+        <v>0.20699532974404633</v>
       </c>
       <c r="X8" s="5">
         <f t="shared" si="3"/>
-        <v>0.25285282773415929</v>
+        <v>0.20699532974404633</v>
       </c>
       <c r="Y8" s="5">
         <f t="shared" si="3"/>
-        <v>0.25285282773415929</v>
+        <v>0.20699532974404633</v>
       </c>
       <c r="Z8" s="5">
         <f t="shared" si="3"/>
-        <v>0.25285282773415929</v>
+        <v>0.20699532974404633</v>
       </c>
       <c r="AA8" s="5">
         <f t="shared" si="3"/>
-        <v>0.25285282773415929</v>
+        <v>0.20699532974404633</v>
       </c>
       <c r="AB8" s="5">
         <f t="shared" si="3"/>
-        <v>0.25285282773415929</v>
+        <v>0.20699532974404633</v>
       </c>
       <c r="AC8" s="5">
         <f t="shared" si="3"/>
-        <v>0.25285282773415929</v>
+        <v>0.20699532974404633</v>
       </c>
       <c r="AD8" s="5">
         <f t="shared" si="3"/>
-        <v>0.25285282773415929</v>
+        <v>0.20699532974404633</v>
       </c>
       <c r="AE8" s="5">
         <f t="shared" si="3"/>
-        <v>0.25285282773415929</v>
+        <v>0.20699532974404633</v>
       </c>
     </row>
   </sheetData>
